--- a/CHIK_MORBID/03_Output/tables/brazil_clustering_ratio_r_PROTOTYPE.xlsx
+++ b/CHIK_MORBID/03_Output/tables/brazil_clustering_ratio_r_PROTOTYPE.xlsx
@@ -6,27 +6,30 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="clustering_ratio_r" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="clustering_weight_lambda" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">age_band_profile</t>
   </si>
   <si>
-    <t xml:space="preserve">r</t>
+    <t xml:space="preserve">lambda_raw</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
-    <t xml:space="preserve">r_lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r_upper</t>
+    <t xml:space="preserve">lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lambda_lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lambda_upper</t>
   </si>
   <si>
     <t xml:space="preserve">0-19</t>
@@ -89,14 +92,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:E6" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:E6"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F6" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:F6"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="age_band_profile"/>
-    <tableColumn id="2" name="r"/>
+    <tableColumn id="2" name="lambda_raw"/>
     <tableColumn id="3" name="n"/>
-    <tableColumn id="4" name="r_lower"/>
-    <tableColumn id="5" name="r_upper"/>
+    <tableColumn id="4" name="lambda"/>
+    <tableColumn id="5" name="lambda_lower"/>
+    <tableColumn id="6" name="lambda_upper"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -400,10 +404,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
         <v>0.368171448927882</v>
@@ -412,15 +419,18 @@
         <v>184881</v>
       </c>
       <c r="D2" t="n">
+        <v>0.368171448927882</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.338470241795575</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.400746108286886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
         <v>0.390602909500151</v>
@@ -429,15 +439,18 @@
         <v>357068</v>
       </c>
       <c r="D3" t="n">
+        <v>0.390602909500151</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.374777667756201</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.407472757254427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
         <v>0.555484411211237</v>
@@ -446,15 +459,18 @@
         <v>340810</v>
       </c>
       <c r="D4" t="n">
+        <v>0.555484411211237</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.546917272425905</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.56397122722484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
         <v>0.675876128028185</v>
@@ -463,15 +479,18 @@
         <v>169183</v>
       </c>
       <c r="D5" t="n">
+        <v>0.675876128028185</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.668321909084515</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.684191658774995</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
         <v>0.762117545309959</v>
@@ -480,9 +499,12 @@
         <v>22854</v>
       </c>
       <c r="D6" t="n">
+        <v>0.762117545309959</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.737014165675262</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.785949859802972</v>
       </c>
     </row>
